--- a/muestras/excel/muestra-extracto-banco.xlsx
+++ b/muestras/excel/muestra-extracto-banco.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,6 +617,105 @@
         <v>-999</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45667</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DEB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LUZ-01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EDESUR servicio electricidad</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45669</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>011</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LUZ-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EDESUR servicio electricidad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Enero refact.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>-15000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DEB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LUZ-03</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EDESUR servicio electricidad</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Enero ajuste</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>-15000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
